--- a/business_forms/036_risk_and_compliance_strategy_advisory_application_form--business_forms.xlsx
+++ b/business_forms/036_risk_and_compliance_strategy_advisory_application_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>risk_and_compliance_strategy_advisory_application_form_page_1</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk And Compliance Strategy Advisory Application Form</t>
+          <t>What is your role in the organization?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,41 +543,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>risk_and_compliance_strategy_advisory_application_form_page_2</t>
+          <t>background_info</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Additional Information</t>
+          <t>Please provide a brief description of the organization's risk and compliance background.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>risk_and_compliance_strategy_advisory_application_form_page_3</t>
+          <t>compliance_strategy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk And Compliance Strategy Advisory Application Form</t>
+          <t>Please describe the organization's current compliance strategy.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>risk_and_compliance_strategy_advisory_application_form_page_4</t>
+          <t>risk_level</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk And Compliance Strategy Advisory Application Form</t>
+          <t>What is the level of risk associated with this compliance issue?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>risk_and_compliance_strategy_advisory_application_form_page_5</t>
+          <t>last_review_date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk And Compliance Strategy Advisory Application Form</t>
+          <t>Date of last review</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>risk_and_compliance_strategy_advisory_application_form_page_6</t>
+          <t>last_review_time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk And Compliance Strategy Advisory Application Form</t>
+          <t>Time of last review</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,62 +658,131 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>risk_and_compliance_strategy_advisory_application_form_page_7</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk And Compliance Strategy Advisory Application Form</t>
+          <t>Please enter your contact information (email, phone number, etc.)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>risk_and_compliance_strategy_advisory_application_form_page_8</t>
+          <t>review_frequency</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>risk_and_compliance_strategy_advisory_application_form_page_8_label</t>
+          <t>How often do you review the risk and compliance issues in the organization?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>risk_and_compliance_strategy_advisory_application_form_page_9</t>
+          <t>frequency_of_risk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>risk_and_compliance_strategy_advisory_application_form_page_9_label</t>
+          <t>How often do the risks associated with this issue occur?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>severity_of_risk</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>How severe is the risk associated with this issue?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>mitigation_plan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Please describe your plan to mitigate the risk associated with this issue.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>additional_comments</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -730,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -758,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>risk_and_compliance_strategy_advisory_application_form_page_3_choices</t>
+          <t>risk_level_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -775,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>risk_and_compliance_strategy_advisory_application_form_page_3_choices</t>
+          <t>risk_level_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -792,7 +861,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>risk_and_compliance_strategy_advisory_application_form_page_3_choices</t>
+          <t>risk_level_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,49 +878,185 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>risk_and_compliance_strategy_advisory_application_form_page_4_choices</t>
+          <t>review_frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>risk_and_compliance_strategy_advisory_application_form_page_4_choices</t>
+          <t>review_frequency_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>risk_and_compliance_strategy_advisory_application_form_page_4_choices</t>
+          <t>review_frequency_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>review_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>review_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>annually</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Annually</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>frequency_of_risk_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>frequently</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Frequently</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>frequency_of_risk_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>frequency_of_risk_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>severity_of_risk_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>severity_of_risk_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>severity_of_risk_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>low</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
